--- a/output/yearly_population_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_18_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7557</v>
+        <v>5376</v>
       </c>
       <c r="C2" t="n">
-        <v>6740</v>
+        <v>7574</v>
       </c>
       <c r="D2" t="n">
-        <v>18007</v>
+        <v>32754</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4054</v>
+        <v>3097</v>
       </c>
       <c r="C3" t="n">
-        <v>5774</v>
+        <v>6383</v>
       </c>
       <c r="D3" t="n">
-        <v>13438</v>
+        <v>14102</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3127</v>
+        <v>2252</v>
       </c>
       <c r="C4" t="n">
-        <v>5357</v>
+        <v>5325</v>
       </c>
       <c r="D4" t="n">
-        <v>7371</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>1459</v>
       </c>
       <c r="C5" t="n">
-        <v>4509</v>
+        <v>4373</v>
       </c>
       <c r="D5" t="n">
-        <v>3003</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1162</v>
+        <v>856</v>
       </c>
       <c r="C6" t="n">
-        <v>3200</v>
+        <v>3546</v>
       </c>
       <c r="D6" t="n">
-        <v>1252</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>546</v>
+        <v>406</v>
       </c>
       <c r="C7" t="n">
-        <v>1984</v>
+        <v>2519</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>1033</v>
+        <v>1319</v>
       </c>
       <c r="D8" t="n">
         <v>429</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>499</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7582</v>
+        <v>5597</v>
       </c>
       <c r="C2" t="n">
-        <v>14280</v>
+        <v>9377</v>
       </c>
       <c r="D2" t="n">
-        <v>32318</v>
+        <v>25980</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4516</v>
+        <v>3346</v>
       </c>
       <c r="C3" t="n">
-        <v>5469</v>
+        <v>6094</v>
       </c>
       <c r="D3" t="n">
-        <v>13156</v>
+        <v>15691</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3041</v>
+        <v>2225</v>
       </c>
       <c r="C4" t="n">
-        <v>5441</v>
+        <v>5711</v>
       </c>
       <c r="D4" t="n">
-        <v>8137</v>
+        <v>7467</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2197</v>
+        <v>1584</v>
       </c>
       <c r="C5" t="n">
-        <v>4754</v>
+        <v>4669</v>
       </c>
       <c r="D5" t="n">
-        <v>3553</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1386</v>
+        <v>1010</v>
       </c>
       <c r="C6" t="n">
-        <v>3747</v>
+        <v>3877</v>
       </c>
       <c r="D6" t="n">
-        <v>1504</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>720</v>
+        <v>536</v>
       </c>
       <c r="C7" t="n">
-        <v>2488</v>
+        <v>2936</v>
       </c>
       <c r="D7" t="n">
-        <v>736</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>227</v>
       </c>
       <c r="C8" t="n">
-        <v>1433</v>
+        <v>1824</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>823</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8298</v>
+        <v>5957</v>
       </c>
       <c r="C2" t="n">
-        <v>9782</v>
+        <v>15675</v>
       </c>
       <c r="D2" t="n">
-        <v>37693</v>
+        <v>22835</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4668</v>
+        <v>3452</v>
       </c>
       <c r="C3" t="n">
-        <v>7966</v>
+        <v>6576</v>
       </c>
       <c r="D3" t="n">
-        <v>14613</v>
+        <v>15921</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>2268</v>
       </c>
       <c r="C4" t="n">
-        <v>5287</v>
+        <v>5699</v>
       </c>
       <c r="D4" t="n">
-        <v>8534</v>
+        <v>8352</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2272</v>
+        <v>1633</v>
       </c>
       <c r="C5" t="n">
-        <v>4893</v>
+        <v>4957</v>
       </c>
       <c r="D5" t="n">
-        <v>4105</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1548</v>
+        <v>1137</v>
       </c>
       <c r="C6" t="n">
-        <v>4120</v>
+        <v>4162</v>
       </c>
       <c r="D6" t="n">
-        <v>1745</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>875</v>
+        <v>644</v>
       </c>
       <c r="C7" t="n">
-        <v>2956</v>
+        <v>3274</v>
       </c>
       <c r="D7" t="n">
-        <v>833</v>
+        <v>769</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="C8" t="n">
-        <v>1821</v>
+        <v>2230</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>948</v>
+        <v>1195</v>
       </c>
       <c r="D9" t="n">
         <v>330</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>422</v>
+        <v>503</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7722</v>
+        <v>5536</v>
       </c>
       <c r="C2" t="n">
-        <v>6730</v>
+        <v>10784</v>
       </c>
       <c r="D2" t="n">
-        <v>30855</v>
+        <v>19032</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5528</v>
+        <v>4108</v>
       </c>
       <c r="C3" t="n">
-        <v>10976</v>
+        <v>10475</v>
       </c>
       <c r="D3" t="n">
-        <v>15948</v>
+        <v>17085</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2099</v>
+        <v>1508</v>
       </c>
       <c r="C4" t="n">
-        <v>7539</v>
+        <v>7822</v>
       </c>
       <c r="D4" t="n">
-        <v>8408</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1430</v>
+        <v>1050</v>
       </c>
       <c r="C5" t="n">
-        <v>4037</v>
+        <v>4078</v>
       </c>
       <c r="D5" t="n">
-        <v>2813</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>808</v>
+        <v>595</v>
       </c>
       <c r="C6" t="n">
-        <v>2896</v>
+        <v>3208</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>1784</v>
+        <v>2185</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>929</v>
+        <v>1171</v>
       </c>
       <c r="D8" t="n">
         <v>323</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>492</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4814</v>
+        <v>3343</v>
       </c>
       <c r="C2" t="n">
-        <v>3282</v>
+        <v>5184</v>
       </c>
       <c r="D2" t="n">
-        <v>22518</v>
+        <v>13313</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5626</v>
+        <v>4072</v>
       </c>
       <c r="C3" t="n">
-        <v>8330</v>
+        <v>9643</v>
       </c>
       <c r="D3" t="n">
-        <v>17209</v>
+        <v>16529</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2913</v>
+        <v>2131</v>
       </c>
       <c r="C4" t="n">
-        <v>9150</v>
+        <v>9081</v>
       </c>
       <c r="D4" t="n">
-        <v>9318</v>
+        <v>9058</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1578</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="n">
-        <v>5558</v>
+        <v>5698</v>
       </c>
       <c r="D5" t="n">
-        <v>3506</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>960</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>3428</v>
+        <v>3665</v>
       </c>
       <c r="D6" t="n">
-        <v>1002</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>2234</v>
+        <v>2647</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>1195</v>
+        <v>1494</v>
       </c>
       <c r="D8" t="n">
         <v>332</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>543</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6401</v>
+        <v>2862</v>
       </c>
       <c r="C2" t="n">
-        <v>6668</v>
+        <v>4991</v>
       </c>
       <c r="D2" t="n">
-        <v>25421</v>
+        <v>12464</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4445</v>
+        <v>3170</v>
       </c>
       <c r="C3" t="n">
-        <v>5337</v>
+        <v>6743</v>
       </c>
       <c r="D3" t="n">
-        <v>16774</v>
+        <v>14980</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3504</v>
+        <v>2548</v>
       </c>
       <c r="C4" t="n">
-        <v>8566</v>
+        <v>9161</v>
       </c>
       <c r="D4" t="n">
-        <v>10322</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>7097</v>
+        <v>7138</v>
       </c>
       <c r="D5" t="n">
-        <v>4292</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1113</v>
+        <v>816</v>
       </c>
       <c r="C6" t="n">
-        <v>4369</v>
+        <v>4563</v>
       </c>
       <c r="D6" t="n">
-        <v>1349</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>517</v>
+        <v>382</v>
       </c>
       <c r="C7" t="n">
-        <v>2758</v>
+        <v>3100</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>1613</v>
+        <v>1960</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>731</v>
+        <v>892</v>
       </c>
       <c r="D9" t="n">
         <v>263</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2495,7 +2495,7 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3823</v>
+        <v>1722</v>
       </c>
       <c r="C2" t="n">
-        <v>3172</v>
+        <v>2394</v>
       </c>
       <c r="D2" t="n">
-        <v>17729</v>
+        <v>8695</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4728</v>
+        <v>2990</v>
       </c>
       <c r="C3" t="n">
-        <v>5619</v>
+        <v>5974</v>
       </c>
       <c r="D3" t="n">
-        <v>17297</v>
+        <v>14382</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3844</v>
+        <v>2789</v>
       </c>
       <c r="C4" t="n">
-        <v>8187</v>
+        <v>9083</v>
       </c>
       <c r="D4" t="n">
-        <v>11102</v>
+        <v>10644</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1965</v>
+        <v>1437</v>
       </c>
       <c r="C5" t="n">
-        <v>8524</v>
+        <v>8625</v>
       </c>
       <c r="D5" t="n">
-        <v>4521</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>677</v>
       </c>
       <c r="C6" t="n">
-        <v>5189</v>
+        <v>5548</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>2917</v>
+        <v>3380</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1190</v>
+        <v>1450</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2792,7 +2792,7 @@
         <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4746</v>
+        <v>2597</v>
       </c>
       <c r="C2" t="n">
-        <v>4102</v>
+        <v>7221</v>
       </c>
       <c r="D2" t="n">
-        <v>21714</v>
+        <v>9734</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3720</v>
+        <v>2105</v>
       </c>
       <c r="C3" t="n">
-        <v>4048</v>
+        <v>3920</v>
       </c>
       <c r="D3" t="n">
-        <v>16359</v>
+        <v>12780</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3659</v>
+        <v>2538</v>
       </c>
       <c r="C4" t="n">
-        <v>6833</v>
+        <v>7461</v>
       </c>
       <c r="D4" t="n">
-        <v>11716</v>
+        <v>10894</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2399</v>
+        <v>1747</v>
       </c>
       <c r="C5" t="n">
-        <v>8279</v>
+        <v>8730</v>
       </c>
       <c r="D5" t="n">
-        <v>5331</v>
+        <v>4949</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1191</v>
+        <v>874</v>
       </c>
       <c r="C6" t="n">
-        <v>6569</v>
+        <v>6822</v>
       </c>
       <c r="D6" t="n">
-        <v>1731</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>3863</v>
+        <v>4294</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1822</v>
+        <v>2158</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3163</v>
+        <v>1702</v>
       </c>
       <c r="C2" t="n">
-        <v>2566</v>
+        <v>4090</v>
       </c>
       <c r="D2" t="n">
-        <v>16421</v>
+        <v>8116</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3541</v>
+        <v>1979</v>
       </c>
       <c r="C3" t="n">
-        <v>3736</v>
+        <v>4762</v>
       </c>
       <c r="D3" t="n">
-        <v>16268</v>
+        <v>11841</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3350</v>
+        <v>2206</v>
       </c>
       <c r="C4" t="n">
-        <v>5791</v>
+        <v>6055</v>
       </c>
       <c r="D4" t="n">
-        <v>12051</v>
+        <v>10902</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2636</v>
+        <v>1896</v>
       </c>
       <c r="C5" t="n">
-        <v>7845</v>
+        <v>8432</v>
       </c>
       <c r="D5" t="n">
-        <v>5945</v>
+        <v>5473</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1394</v>
+        <v>1022</v>
       </c>
       <c r="C6" t="n">
-        <v>7356</v>
+        <v>7679</v>
       </c>
       <c r="D6" t="n">
-        <v>2020</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>4762</v>
+        <v>5181</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2316</v>
+        <v>2695</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>665</v>
+        <v>785</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4414</v>
+        <v>2849</v>
       </c>
       <c r="C2" t="n">
-        <v>7565</v>
+        <v>8803</v>
       </c>
       <c r="D2" t="n">
-        <v>14243</v>
+        <v>7938</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2871</v>
+        <v>1586</v>
       </c>
       <c r="C3" t="n">
-        <v>2927</v>
+        <v>4045</v>
       </c>
       <c r="D3" t="n">
-        <v>15245</v>
+        <v>10636</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2968</v>
+        <v>1849</v>
       </c>
       <c r="C4" t="n">
-        <v>4822</v>
+        <v>5395</v>
       </c>
       <c r="D4" t="n">
-        <v>12291</v>
+        <v>10705</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2646</v>
+        <v>1846</v>
       </c>
       <c r="C5" t="n">
-        <v>6873</v>
+        <v>7321</v>
       </c>
       <c r="D5" t="n">
-        <v>6584</v>
+        <v>6036</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1670</v>
+        <v>1205</v>
       </c>
       <c r="C6" t="n">
-        <v>7478</v>
+        <v>7897</v>
       </c>
       <c r="D6" t="n">
-        <v>2483</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>560</v>
+        <v>421</v>
       </c>
       <c r="C7" t="n">
-        <v>5700</v>
+        <v>6084</v>
       </c>
       <c r="D7" t="n">
-        <v>889</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>3176</v>
+        <v>3546</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1189</v>
+        <v>1410</v>
       </c>
       <c r="D9" t="n">
         <v>296</v>
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>396</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
         <v>139</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7952</v>
+        <v>4683</v>
       </c>
       <c r="C2" t="n">
-        <v>10064</v>
+        <v>12874</v>
       </c>
       <c r="D2" t="n">
-        <v>10342</v>
+        <v>10626</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3193</v>
+        <v>2057</v>
       </c>
       <c r="C2" t="n">
-        <v>4417</v>
+        <v>5070</v>
       </c>
       <c r="D2" t="n">
-        <v>10596</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3760</v>
+        <v>2177</v>
       </c>
       <c r="C3" t="n">
-        <v>4191</v>
+        <v>5466</v>
       </c>
       <c r="D3" t="n">
-        <v>16258</v>
+        <v>11374</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3963</v>
+        <v>2648</v>
       </c>
       <c r="C4" t="n">
-        <v>7059</v>
+        <v>7886</v>
       </c>
       <c r="D4" t="n">
-        <v>12553</v>
+        <v>11006</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1591</v>
+        <v>1147</v>
       </c>
       <c r="C5" t="n">
-        <v>10356</v>
+        <v>10977</v>
       </c>
       <c r="D5" t="n">
-        <v>5957</v>
+        <v>5479</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>517</v>
+        <v>389</v>
       </c>
       <c r="C6" t="n">
-        <v>6978</v>
+        <v>7432</v>
       </c>
       <c r="D6" t="n">
-        <v>1974</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>3112</v>
+        <v>3475</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1165</v>
+        <v>1381</v>
       </c>
       <c r="D8" t="n">
         <v>290</v>
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>388</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
         <v>136</v>
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7366</v>
+        <v>5964</v>
       </c>
       <c r="C2" t="n">
-        <v>6637</v>
+        <v>10192</v>
       </c>
       <c r="D2" t="n">
-        <v>27524</v>
+        <v>10839</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3377</v>
+        <v>1991</v>
       </c>
       <c r="C3" t="n">
-        <v>5072</v>
+        <v>6488</v>
       </c>
       <c r="D3" t="n">
-        <v>2376</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4958</v>
+        <v>4590</v>
       </c>
       <c r="C2" t="n">
-        <v>6341</v>
+        <v>5199</v>
       </c>
       <c r="D2" t="n">
-        <v>22914</v>
+        <v>17825</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4415</v>
+        <v>3264</v>
       </c>
       <c r="C3" t="n">
-        <v>5137</v>
+        <v>7402</v>
       </c>
       <c r="D3" t="n">
-        <v>6425</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1501</v>
+        <v>899</v>
       </c>
       <c r="C4" t="n">
-        <v>3016</v>
+        <v>3845</v>
       </c>
       <c r="D4" t="n">
-        <v>1660</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
         <v>225</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5785</v>
+        <v>3999</v>
       </c>
       <c r="C2" t="n">
-        <v>3981</v>
+        <v>5581</v>
       </c>
       <c r="D2" t="n">
-        <v>25290</v>
+        <v>22868</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3859</v>
+        <v>3217</v>
       </c>
       <c r="C3" t="n">
-        <v>5013</v>
+        <v>5396</v>
       </c>
       <c r="D3" t="n">
-        <v>8600</v>
+        <v>5662</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>1768</v>
       </c>
       <c r="C4" t="n">
-        <v>4134</v>
+        <v>5708</v>
       </c>
       <c r="D4" t="n">
-        <v>2524</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>665</v>
+        <v>422</v>
       </c>
       <c r="C5" t="n">
-        <v>1718</v>
+        <v>2201</v>
       </c>
       <c r="D5" t="n">
-        <v>1245</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6783</v>
+        <v>4341</v>
       </c>
       <c r="C2" t="n">
-        <v>10740</v>
+        <v>6937</v>
       </c>
       <c r="D2" t="n">
-        <v>23589</v>
+        <v>21714</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3904</v>
+        <v>2951</v>
       </c>
       <c r="C3" t="n">
-        <v>3917</v>
+        <v>4786</v>
       </c>
       <c r="D3" t="n">
-        <v>10531</v>
+        <v>7878</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2697</v>
+        <v>2089</v>
       </c>
       <c r="C4" t="n">
-        <v>4512</v>
+        <v>5369</v>
       </c>
       <c r="D4" t="n">
-        <v>3555</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1281</v>
+        <v>900</v>
       </c>
       <c r="C5" t="n">
-        <v>2895</v>
+        <v>3973</v>
       </c>
       <c r="D5" t="n">
-        <v>1416</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>342</v>
+        <v>246</v>
       </c>
       <c r="C6" t="n">
-        <v>1008</v>
+        <v>1248</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7217</v>
+        <v>5273</v>
       </c>
       <c r="C2" t="n">
-        <v>7047</v>
+        <v>7439</v>
       </c>
       <c r="D2" t="n">
-        <v>19380</v>
+        <v>27528</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3822</v>
+        <v>2624</v>
       </c>
       <c r="C3" t="n">
-        <v>6013</v>
+        <v>4807</v>
       </c>
       <c r="D3" t="n">
-        <v>11078</v>
+        <v>8868</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>1546</v>
       </c>
       <c r="C4" t="n">
-        <v>3427</v>
+        <v>4133</v>
       </c>
       <c r="D4" t="n">
-        <v>4117</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1039</v>
+        <v>770</v>
       </c>
       <c r="C5" t="n">
-        <v>2691</v>
+        <v>3384</v>
       </c>
       <c r="D5" t="n">
-        <v>1400</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>375</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>1306</v>
+        <v>1747</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,7 +5899,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6274</v>
+        <v>4605</v>
       </c>
       <c r="C2" t="n">
-        <v>7565</v>
+        <v>8165</v>
       </c>
       <c r="D2" t="n">
-        <v>25271</v>
+        <v>24515</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4565</v>
+        <v>3266</v>
       </c>
       <c r="C3" t="n">
-        <v>5688</v>
+        <v>5502</v>
       </c>
       <c r="D3" t="n">
-        <v>11657</v>
+        <v>11350</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2555</v>
+        <v>1821</v>
       </c>
       <c r="C4" t="n">
-        <v>4862</v>
+        <v>4408</v>
       </c>
       <c r="D4" t="n">
-        <v>5395</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1351</v>
+        <v>1021</v>
       </c>
       <c r="C5" t="n">
-        <v>3066</v>
+        <v>3752</v>
       </c>
       <c r="D5" t="n">
-        <v>1865</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>654</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>2074</v>
+        <v>2652</v>
       </c>
       <c r="D6" t="n">
-        <v>887</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>916</v>
+        <v>1194</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5513</v>
+        <v>4443</v>
       </c>
       <c r="C2" t="n">
-        <v>7445</v>
+        <v>8665</v>
       </c>
       <c r="D2" t="n">
-        <v>22287</v>
+        <v>28839</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4431</v>
+        <v>3215</v>
       </c>
       <c r="C3" t="n">
-        <v>5803</v>
+        <v>6006</v>
       </c>
       <c r="D3" t="n">
-        <v>12995</v>
+        <v>12639</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3020</v>
+        <v>2157</v>
       </c>
       <c r="C4" t="n">
-        <v>5220</v>
+        <v>4925</v>
       </c>
       <c r="D4" t="n">
-        <v>6433</v>
+        <v>5364</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1709</v>
+        <v>1248</v>
       </c>
       <c r="C5" t="n">
-        <v>3967</v>
+        <v>3990</v>
       </c>
       <c r="D5" t="n">
-        <v>2452</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>900</v>
+        <v>672</v>
       </c>
       <c r="C6" t="n">
-        <v>2544</v>
+        <v>3202</v>
       </c>
       <c r="D6" t="n">
-        <v>1035</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>1517</v>
+        <v>1950</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>781</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>

--- a/output/yearly_population_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_18_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5376</v>
+        <v>5658</v>
       </c>
       <c r="C2" t="n">
-        <v>7574</v>
+        <v>12439</v>
       </c>
       <c r="D2" t="n">
-        <v>32754</v>
+        <v>19881</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3097</v>
+        <v>3530</v>
       </c>
       <c r="C3" t="n">
-        <v>6383</v>
+        <v>8509</v>
       </c>
       <c r="D3" t="n">
-        <v>14102</v>
+        <v>14423</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2252</v>
+        <v>2742</v>
       </c>
       <c r="C4" t="n">
-        <v>5325</v>
+        <v>6942</v>
       </c>
       <c r="D4" t="n">
-        <v>6406</v>
+        <v>7473</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1459</v>
+        <v>1908</v>
       </c>
       <c r="C5" t="n">
-        <v>4373</v>
+        <v>5323</v>
       </c>
       <c r="D5" t="n">
-        <v>2486</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>1144</v>
       </c>
       <c r="C6" t="n">
-        <v>3546</v>
+        <v>3489</v>
       </c>
       <c r="D6" t="n">
-        <v>1095</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>406</v>
+        <v>573</v>
       </c>
       <c r="C7" t="n">
-        <v>2519</v>
+        <v>1941</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C8" t="n">
-        <v>1319</v>
+        <v>901</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
         <v>245</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5597</v>
+        <v>6948</v>
       </c>
       <c r="C2" t="n">
-        <v>9377</v>
+        <v>10223</v>
       </c>
       <c r="D2" t="n">
-        <v>25980</v>
+        <v>24429</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3346</v>
+        <v>3615</v>
       </c>
       <c r="C3" t="n">
-        <v>6094</v>
+        <v>9024</v>
       </c>
       <c r="D3" t="n">
-        <v>15691</v>
+        <v>14175</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2225</v>
+        <v>2628</v>
       </c>
       <c r="C4" t="n">
-        <v>5711</v>
+        <v>7453</v>
       </c>
       <c r="D4" t="n">
-        <v>7467</v>
+        <v>8241</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1584</v>
+        <v>2021</v>
       </c>
       <c r="C5" t="n">
-        <v>4669</v>
+        <v>5942</v>
       </c>
       <c r="D5" t="n">
-        <v>2988</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1010</v>
+        <v>1328</v>
       </c>
       <c r="C6" t="n">
-        <v>3877</v>
+        <v>4214</v>
       </c>
       <c r="D6" t="n">
-        <v>1293</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>536</v>
+        <v>724</v>
       </c>
       <c r="C7" t="n">
-        <v>2936</v>
+        <v>2607</v>
       </c>
       <c r="D7" t="n">
-        <v>694</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="C8" t="n">
-        <v>1824</v>
+        <v>1319</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C9" t="n">
-        <v>823</v>
+        <v>592</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5957</v>
+        <v>7513</v>
       </c>
       <c r="C2" t="n">
-        <v>15675</v>
+        <v>11071</v>
       </c>
       <c r="D2" t="n">
-        <v>22835</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3452</v>
+        <v>3972</v>
       </c>
       <c r="C3" t="n">
-        <v>6576</v>
+        <v>8454</v>
       </c>
       <c r="D3" t="n">
-        <v>15921</v>
+        <v>14498</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2268</v>
+        <v>2564</v>
       </c>
       <c r="C4" t="n">
-        <v>5699</v>
+        <v>7874</v>
       </c>
       <c r="D4" t="n">
-        <v>8352</v>
+        <v>8844</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>2016</v>
       </c>
       <c r="C5" t="n">
-        <v>4957</v>
+        <v>6370</v>
       </c>
       <c r="D5" t="n">
-        <v>3542</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1137</v>
+        <v>1457</v>
       </c>
       <c r="C6" t="n">
-        <v>4162</v>
+        <v>4857</v>
       </c>
       <c r="D6" t="n">
-        <v>1491</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>644</v>
+        <v>866</v>
       </c>
       <c r="C7" t="n">
-        <v>3274</v>
+        <v>3194</v>
       </c>
       <c r="D7" t="n">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>303</v>
+        <v>411</v>
       </c>
       <c r="C8" t="n">
-        <v>2230</v>
+        <v>1785</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C9" t="n">
-        <v>1195</v>
+        <v>849</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>503</v>
+        <v>388</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
         <v>207</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5536</v>
+        <v>6933</v>
       </c>
       <c r="C2" t="n">
-        <v>10784</v>
+        <v>7705</v>
       </c>
       <c r="D2" t="n">
-        <v>19032</v>
+        <v>19775</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4108</v>
+        <v>4654</v>
       </c>
       <c r="C3" t="n">
-        <v>10475</v>
+        <v>12668</v>
       </c>
       <c r="D3" t="n">
-        <v>17085</v>
+        <v>15939</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1508</v>
+        <v>1862</v>
       </c>
       <c r="C4" t="n">
-        <v>7822</v>
+        <v>10272</v>
       </c>
       <c r="D4" t="n">
-        <v>7900</v>
+        <v>8511</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1050</v>
+        <v>1346</v>
       </c>
       <c r="C5" t="n">
-        <v>4078</v>
+        <v>4759</v>
       </c>
       <c r="D5" t="n">
-        <v>2413</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>595</v>
+        <v>800</v>
       </c>
       <c r="C6" t="n">
-        <v>3208</v>
+        <v>3130</v>
       </c>
       <c r="D6" t="n">
-        <v>753</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>379</v>
       </c>
       <c r="C7" t="n">
-        <v>2185</v>
+        <v>1749</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1171</v>
+        <v>832</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>492</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
         <v>202</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
         <v>125</v>
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3343</v>
+        <v>4356</v>
       </c>
       <c r="C2" t="n">
-        <v>5184</v>
+        <v>3902</v>
       </c>
       <c r="D2" t="n">
-        <v>13313</v>
+        <v>14150</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4072</v>
+        <v>4819</v>
       </c>
       <c r="C3" t="n">
-        <v>9643</v>
+        <v>9527</v>
       </c>
       <c r="D3" t="n">
-        <v>16529</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2131</v>
+        <v>2514</v>
       </c>
       <c r="C4" t="n">
-        <v>9081</v>
+        <v>11533</v>
       </c>
       <c r="D4" t="n">
-        <v>9058</v>
+        <v>9485</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1152</v>
+        <v>1475</v>
       </c>
       <c r="C5" t="n">
-        <v>5698</v>
+        <v>7012</v>
       </c>
       <c r="D5" t="n">
-        <v>3093</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>706</v>
+        <v>930</v>
       </c>
       <c r="C6" t="n">
-        <v>3665</v>
+        <v>3868</v>
       </c>
       <c r="D6" t="n">
-        <v>909</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>2647</v>
+        <v>2237</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>1494</v>
+        <v>1106</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>543</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2862</v>
+        <v>4181</v>
       </c>
       <c r="C2" t="n">
-        <v>4991</v>
+        <v>5648</v>
       </c>
       <c r="D2" t="n">
-        <v>12464</v>
+        <v>14637</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3170</v>
+        <v>3892</v>
       </c>
       <c r="C3" t="n">
-        <v>6743</v>
+        <v>6225</v>
       </c>
       <c r="D3" t="n">
-        <v>14980</v>
+        <v>14430</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2548</v>
+        <v>2991</v>
       </c>
       <c r="C4" t="n">
-        <v>9161</v>
+        <v>10349</v>
       </c>
       <c r="D4" t="n">
-        <v>10001</v>
+        <v>10210</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>1692</v>
       </c>
       <c r="C5" t="n">
-        <v>7138</v>
+        <v>8906</v>
       </c>
       <c r="D5" t="n">
-        <v>3915</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>816</v>
+        <v>1056</v>
       </c>
       <c r="C6" t="n">
-        <v>4563</v>
+        <v>5227</v>
       </c>
       <c r="D6" t="n">
-        <v>1211</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>382</v>
+        <v>506</v>
       </c>
       <c r="C7" t="n">
-        <v>3100</v>
+        <v>2907</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>1960</v>
+        <v>1559</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>892</v>
+        <v>672</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1722</v>
+        <v>2551</v>
       </c>
       <c r="C2" t="n">
-        <v>2394</v>
+        <v>2751</v>
       </c>
       <c r="D2" t="n">
-        <v>8695</v>
+        <v>10203</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2990</v>
+        <v>3821</v>
       </c>
       <c r="C3" t="n">
-        <v>5974</v>
+        <v>5871</v>
       </c>
       <c r="D3" t="n">
-        <v>14382</v>
+        <v>14128</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>3290</v>
       </c>
       <c r="C4" t="n">
-        <v>9083</v>
+        <v>9860</v>
       </c>
       <c r="D4" t="n">
-        <v>10644</v>
+        <v>10794</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1437</v>
+        <v>1785</v>
       </c>
       <c r="C5" t="n">
-        <v>8625</v>
+        <v>10553</v>
       </c>
       <c r="D5" t="n">
-        <v>4139</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>677</v>
+        <v>877</v>
       </c>
       <c r="C6" t="n">
-        <v>5548</v>
+        <v>6074</v>
       </c>
       <c r="D6" t="n">
-        <v>1192</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>3380</v>
+        <v>2949</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1450</v>
+        <v>1116</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2597</v>
+        <v>3727</v>
       </c>
       <c r="C2" t="n">
-        <v>7221</v>
+        <v>4398</v>
       </c>
       <c r="D2" t="n">
-        <v>9734</v>
+        <v>13070</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2105</v>
+        <v>2814</v>
       </c>
       <c r="C3" t="n">
-        <v>3920</v>
+        <v>4043</v>
       </c>
       <c r="D3" t="n">
-        <v>12780</v>
+        <v>12698</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2538</v>
+        <v>3087</v>
       </c>
       <c r="C4" t="n">
-        <v>7461</v>
+        <v>7855</v>
       </c>
       <c r="D4" t="n">
-        <v>10894</v>
+        <v>10977</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1747</v>
+        <v>2107</v>
       </c>
       <c r="C5" t="n">
-        <v>8730</v>
+        <v>10135</v>
       </c>
       <c r="D5" t="n">
-        <v>4949</v>
+        <v>5187</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>874</v>
+        <v>1094</v>
       </c>
       <c r="C6" t="n">
-        <v>6822</v>
+        <v>7886</v>
       </c>
       <c r="D6" t="n">
-        <v>1572</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>4294</v>
+        <v>4199</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>2158</v>
+        <v>1766</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>697</v>
+        <v>542</v>
       </c>
       <c r="D9" t="n">
         <v>292</v>
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1702</v>
+        <v>2495</v>
       </c>
       <c r="C2" t="n">
-        <v>4090</v>
+        <v>2977</v>
       </c>
       <c r="D2" t="n">
-        <v>8116</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1979</v>
+        <v>2710</v>
       </c>
       <c r="C3" t="n">
-        <v>4762</v>
+        <v>3841</v>
       </c>
       <c r="D3" t="n">
-        <v>11841</v>
+        <v>12069</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2206</v>
+        <v>2749</v>
       </c>
       <c r="C4" t="n">
-        <v>6055</v>
+        <v>6378</v>
       </c>
       <c r="D4" t="n">
-        <v>10902</v>
+        <v>10963</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1896</v>
+        <v>2285</v>
       </c>
       <c r="C5" t="n">
-        <v>8432</v>
+        <v>9525</v>
       </c>
       <c r="D5" t="n">
-        <v>5473</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1022</v>
+        <v>1255</v>
       </c>
       <c r="C6" t="n">
-        <v>7679</v>
+        <v>8869</v>
       </c>
       <c r="D6" t="n">
-        <v>1891</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>5181</v>
+        <v>5316</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2695</v>
+        <v>2286</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>785</v>
+        <v>598</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2849</v>
+        <v>3614</v>
       </c>
       <c r="C2" t="n">
-        <v>8803</v>
+        <v>4838</v>
       </c>
       <c r="D2" t="n">
-        <v>7938</v>
+        <v>16469</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1586</v>
+        <v>2222</v>
       </c>
       <c r="C3" t="n">
-        <v>4045</v>
+        <v>3162</v>
       </c>
       <c r="D3" t="n">
-        <v>10636</v>
+        <v>11088</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1849</v>
+        <v>2377</v>
       </c>
       <c r="C4" t="n">
-        <v>5395</v>
+        <v>5222</v>
       </c>
       <c r="D4" t="n">
-        <v>10705</v>
+        <v>10778</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>2248</v>
       </c>
       <c r="C5" t="n">
-        <v>7321</v>
+        <v>8118</v>
       </c>
       <c r="D5" t="n">
-        <v>6036</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1205</v>
+        <v>1458</v>
       </c>
       <c r="C6" t="n">
-        <v>7897</v>
+        <v>9037</v>
       </c>
       <c r="D6" t="n">
-        <v>2313</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>518</v>
       </c>
       <c r="C7" t="n">
-        <v>6084</v>
+        <v>6567</v>
       </c>
       <c r="D7" t="n">
-        <v>839</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>3546</v>
+        <v>3317</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1410</v>
+        <v>1110</v>
       </c>
       <c r="D9" t="n">
         <v>296</v>
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>396</v>
+        <v>326</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4683</v>
+        <v>8453</v>
       </c>
       <c r="C2" t="n">
-        <v>12874</v>
+        <v>8622</v>
       </c>
       <c r="D2" t="n">
-        <v>10626</v>
+        <v>16152</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2057</v>
+        <v>2641</v>
       </c>
       <c r="C2" t="n">
-        <v>5070</v>
+        <v>2865</v>
       </c>
       <c r="D2" t="n">
-        <v>5905</v>
+        <v>12252</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2177</v>
+        <v>2943</v>
       </c>
       <c r="C3" t="n">
-        <v>5466</v>
+        <v>3849</v>
       </c>
       <c r="D3" t="n">
-        <v>11374</v>
+        <v>12394</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2648</v>
+        <v>3291</v>
       </c>
       <c r="C4" t="n">
-        <v>7886</v>
+        <v>7855</v>
       </c>
       <c r="D4" t="n">
-        <v>11006</v>
+        <v>10998</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1147</v>
+        <v>1367</v>
       </c>
       <c r="C5" t="n">
-        <v>10977</v>
+        <v>12405</v>
       </c>
       <c r="D5" t="n">
-        <v>5479</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>389</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>7432</v>
+        <v>8029</v>
       </c>
       <c r="D6" t="n">
-        <v>1848</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>3475</v>
+        <v>3250</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1381</v>
+        <v>1087</v>
       </c>
       <c r="D8" t="n">
         <v>290</v>
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>388</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5964</v>
+        <v>7464</v>
       </c>
       <c r="C2" t="n">
-        <v>10192</v>
+        <v>4623</v>
       </c>
       <c r="D2" t="n">
-        <v>10839</v>
+        <v>15148</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1991</v>
+        <v>3589</v>
       </c>
       <c r="C3" t="n">
-        <v>6488</v>
+        <v>4345</v>
       </c>
       <c r="D3" t="n">
-        <v>2424</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4590</v>
+        <v>5184</v>
       </c>
       <c r="C2" t="n">
-        <v>5199</v>
+        <v>9084</v>
       </c>
       <c r="D2" t="n">
-        <v>17825</v>
+        <v>17102</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3264</v>
+        <v>4543</v>
       </c>
       <c r="C3" t="n">
-        <v>7402</v>
+        <v>3882</v>
       </c>
       <c r="D3" t="n">
-        <v>3659</v>
+        <v>5087</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>899</v>
+        <v>1593</v>
       </c>
       <c r="C4" t="n">
-        <v>3845</v>
+        <v>2590</v>
       </c>
       <c r="D4" t="n">
-        <v>1669</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="5">
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3999</v>
+        <v>5527</v>
       </c>
       <c r="C2" t="n">
-        <v>5581</v>
+        <v>6370</v>
       </c>
       <c r="D2" t="n">
-        <v>22868</v>
+        <v>28699</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3217</v>
+        <v>4006</v>
       </c>
       <c r="C3" t="n">
-        <v>5396</v>
+        <v>5852</v>
       </c>
       <c r="D3" t="n">
-        <v>5662</v>
+        <v>6643</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1768</v>
+        <v>2615</v>
       </c>
       <c r="C4" t="n">
-        <v>5708</v>
+        <v>3230</v>
       </c>
       <c r="D4" t="n">
-        <v>2000</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>422</v>
+        <v>700</v>
       </c>
       <c r="C5" t="n">
-        <v>2201</v>
+        <v>1514</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="6">
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5319,7 +5319,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4341</v>
+        <v>5707</v>
       </c>
       <c r="C2" t="n">
-        <v>6937</v>
+        <v>11440</v>
       </c>
       <c r="D2" t="n">
-        <v>21714</v>
+        <v>24770</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2951</v>
+        <v>3877</v>
       </c>
       <c r="C3" t="n">
-        <v>4786</v>
+        <v>5330</v>
       </c>
       <c r="D3" t="n">
-        <v>7878</v>
+        <v>9527</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2089</v>
+        <v>2795</v>
       </c>
       <c r="C4" t="n">
-        <v>5369</v>
+        <v>4516</v>
       </c>
       <c r="D4" t="n">
-        <v>2607</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>900</v>
+        <v>1371</v>
       </c>
       <c r="C5" t="n">
-        <v>3973</v>
+        <v>2372</v>
       </c>
       <c r="D5" t="n">
-        <v>1317</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>246</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>1248</v>
+        <v>905</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
         <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5273</v>
+        <v>6222</v>
       </c>
       <c r="C2" t="n">
-        <v>7439</v>
+        <v>9737</v>
       </c>
       <c r="D2" t="n">
-        <v>27528</v>
+        <v>29685</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2624</v>
+        <v>3493</v>
       </c>
       <c r="C3" t="n">
-        <v>4807</v>
+        <v>6879</v>
       </c>
       <c r="D3" t="n">
-        <v>8868</v>
+        <v>10512</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1546</v>
+        <v>2047</v>
       </c>
       <c r="C4" t="n">
-        <v>4133</v>
+        <v>4021</v>
       </c>
       <c r="D4" t="n">
-        <v>3044</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>770</v>
+        <v>1083</v>
       </c>
       <c r="C5" t="n">
-        <v>3384</v>
+        <v>2545</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>270</v>
+        <v>406</v>
       </c>
       <c r="C6" t="n">
-        <v>1747</v>
+        <v>1097</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>496</v>
+        <v>390</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4605</v>
+        <v>5122</v>
       </c>
       <c r="C2" t="n">
-        <v>8165</v>
+        <v>10143</v>
       </c>
       <c r="D2" t="n">
-        <v>24515</v>
+        <v>25990</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3266</v>
+        <v>4016</v>
       </c>
       <c r="C3" t="n">
-        <v>5502</v>
+        <v>7339</v>
       </c>
       <c r="D3" t="n">
-        <v>11350</v>
+        <v>12959</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1821</v>
+        <v>2419</v>
       </c>
       <c r="C4" t="n">
-        <v>4408</v>
+        <v>5638</v>
       </c>
       <c r="D4" t="n">
-        <v>4096</v>
+        <v>4927</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1021</v>
+        <v>1382</v>
       </c>
       <c r="C5" t="n">
-        <v>3752</v>
+        <v>3317</v>
       </c>
       <c r="D5" t="n">
-        <v>1538</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>480</v>
+        <v>689</v>
       </c>
       <c r="C6" t="n">
-        <v>2652</v>
+        <v>1903</v>
       </c>
       <c r="D6" t="n">
-        <v>843</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="C7" t="n">
-        <v>1194</v>
+        <v>784</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>369</v>
+        <v>312</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4443</v>
+        <v>4951</v>
       </c>
       <c r="C2" t="n">
-        <v>8665</v>
+        <v>11913</v>
       </c>
       <c r="D2" t="n">
-        <v>28839</v>
+        <v>23031</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3215</v>
+        <v>3746</v>
       </c>
       <c r="C3" t="n">
-        <v>6006</v>
+        <v>7665</v>
       </c>
       <c r="D3" t="n">
-        <v>12639</v>
+        <v>14110</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2157</v>
+        <v>2755</v>
       </c>
       <c r="C4" t="n">
-        <v>4925</v>
+        <v>6467</v>
       </c>
       <c r="D4" t="n">
-        <v>5364</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1248</v>
+        <v>1650</v>
       </c>
       <c r="C5" t="n">
-        <v>3990</v>
+        <v>4495</v>
       </c>
       <c r="D5" t="n">
-        <v>1957</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>672</v>
+        <v>937</v>
       </c>
       <c r="C6" t="n">
-        <v>3202</v>
+        <v>2614</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>397</v>
       </c>
       <c r="C7" t="n">
-        <v>1950</v>
+        <v>1346</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>781</v>
+        <v>547</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_18_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5658</v>
+        <v>1072</v>
       </c>
       <c r="C2" t="n">
-        <v>12439</v>
+        <v>2376</v>
       </c>
       <c r="D2" t="n">
-        <v>19881</v>
+        <v>16238</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3530</v>
+        <v>1906</v>
       </c>
       <c r="C3" t="n">
-        <v>8509</v>
+        <v>5251</v>
       </c>
       <c r="D3" t="n">
-        <v>14423</v>
+        <v>18693</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742</v>
+        <v>1270</v>
       </c>
       <c r="C4" t="n">
-        <v>6942</v>
+        <v>6232</v>
       </c>
       <c r="D4" t="n">
-        <v>7473</v>
+        <v>9108</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1908</v>
+        <v>607</v>
       </c>
       <c r="C5" t="n">
-        <v>5323</v>
+        <v>3414</v>
       </c>
       <c r="D5" t="n">
-        <v>2832</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1144</v>
+        <v>264</v>
       </c>
       <c r="C6" t="n">
-        <v>3489</v>
+        <v>1327</v>
       </c>
       <c r="D6" t="n">
-        <v>1197</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>573</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>1941</v>
+        <v>574</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>214</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>901</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6948</v>
+        <v>711</v>
       </c>
       <c r="C2" t="n">
-        <v>10223</v>
+        <v>4227</v>
       </c>
       <c r="D2" t="n">
-        <v>24429</v>
+        <v>16784</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3615</v>
+        <v>1272</v>
       </c>
       <c r="C3" t="n">
-        <v>9024</v>
+        <v>3270</v>
       </c>
       <c r="D3" t="n">
-        <v>14175</v>
+        <v>17133</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2628</v>
+        <v>1369</v>
       </c>
       <c r="C4" t="n">
-        <v>7453</v>
+        <v>5565</v>
       </c>
       <c r="D4" t="n">
-        <v>8241</v>
+        <v>10579</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2021</v>
+        <v>812</v>
       </c>
       <c r="C5" t="n">
-        <v>5942</v>
+        <v>4863</v>
       </c>
       <c r="D5" t="n">
-        <v>3458</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1328</v>
+        <v>378</v>
       </c>
       <c r="C6" t="n">
-        <v>4214</v>
+        <v>2367</v>
       </c>
       <c r="D6" t="n">
-        <v>1404</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>724</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>2607</v>
+        <v>940</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1319</v>
+        <v>447</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7513</v>
+        <v>372</v>
       </c>
       <c r="C2" t="n">
-        <v>11071</v>
+        <v>1741</v>
       </c>
       <c r="D2" t="n">
-        <v>23850</v>
+        <v>11376</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3972</v>
+        <v>1066</v>
       </c>
       <c r="C3" t="n">
-        <v>8454</v>
+        <v>3477</v>
       </c>
       <c r="D3" t="n">
-        <v>14498</v>
+        <v>16622</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2564</v>
+        <v>1495</v>
       </c>
       <c r="C4" t="n">
-        <v>7874</v>
+        <v>5111</v>
       </c>
       <c r="D4" t="n">
-        <v>8844</v>
+        <v>11520</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2016</v>
+        <v>815</v>
       </c>
       <c r="C5" t="n">
-        <v>6370</v>
+        <v>5657</v>
       </c>
       <c r="D5" t="n">
-        <v>3962</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1457</v>
+        <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>4857</v>
+        <v>3119</v>
       </c>
       <c r="D6" t="n">
-        <v>1661</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>866</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>3194</v>
+        <v>957</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>411</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1785</v>
+        <v>467</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>849</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>388</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6933</v>
+        <v>888</v>
       </c>
       <c r="C2" t="n">
-        <v>7705</v>
+        <v>3701</v>
       </c>
       <c r="D2" t="n">
-        <v>19775</v>
+        <v>13372</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4654</v>
+        <v>639</v>
       </c>
       <c r="C3" t="n">
-        <v>12668</v>
+        <v>2262</v>
       </c>
       <c r="D3" t="n">
-        <v>15939</v>
+        <v>14654</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1862</v>
+        <v>1160</v>
       </c>
       <c r="C4" t="n">
-        <v>10272</v>
+        <v>4175</v>
       </c>
       <c r="D4" t="n">
-        <v>8511</v>
+        <v>12210</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1346</v>
+        <v>996</v>
       </c>
       <c r="C5" t="n">
-        <v>4759</v>
+        <v>5315</v>
       </c>
       <c r="D5" t="n">
-        <v>2692</v>
+        <v>5323</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>473</v>
       </c>
       <c r="C6" t="n">
-        <v>3130</v>
+        <v>4365</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>1749</v>
+        <v>1950</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>832</v>
+        <v>677</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4356</v>
+        <v>510</v>
       </c>
       <c r="C2" t="n">
-        <v>3902</v>
+        <v>1802</v>
       </c>
       <c r="D2" t="n">
-        <v>14150</v>
+        <v>9898</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4819</v>
+        <v>639</v>
       </c>
       <c r="C3" t="n">
-        <v>9527</v>
+        <v>2625</v>
       </c>
       <c r="D3" t="n">
-        <v>15695</v>
+        <v>13635</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2514</v>
+        <v>907</v>
       </c>
       <c r="C4" t="n">
-        <v>11533</v>
+        <v>3290</v>
       </c>
       <c r="D4" t="n">
-        <v>9485</v>
+        <v>12331</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1475</v>
+        <v>1031</v>
       </c>
       <c r="C5" t="n">
-        <v>7012</v>
+        <v>4916</v>
       </c>
       <c r="D5" t="n">
-        <v>3332</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>580</v>
       </c>
       <c r="C6" t="n">
-        <v>3868</v>
+        <v>4941</v>
       </c>
       <c r="D6" t="n">
-        <v>962</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>2237</v>
+        <v>2816</v>
       </c>
       <c r="D7" t="n">
-        <v>510</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1106</v>
+        <v>1017</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4181</v>
+        <v>1295</v>
       </c>
       <c r="C2" t="n">
-        <v>5648</v>
+        <v>12724</v>
       </c>
       <c r="D2" t="n">
-        <v>14637</v>
+        <v>10196</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3892</v>
+        <v>491</v>
       </c>
       <c r="C3" t="n">
-        <v>6225</v>
+        <v>1959</v>
       </c>
       <c r="D3" t="n">
-        <v>14430</v>
+        <v>12289</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2991</v>
+        <v>692</v>
       </c>
       <c r="C4" t="n">
-        <v>10349</v>
+        <v>2889</v>
       </c>
       <c r="D4" t="n">
-        <v>10210</v>
+        <v>12050</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1692</v>
+        <v>909</v>
       </c>
       <c r="C5" t="n">
-        <v>8906</v>
+        <v>4080</v>
       </c>
       <c r="D5" t="n">
-        <v>4175</v>
+        <v>7002</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1056</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>5227</v>
+        <v>4881</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>506</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>2907</v>
+        <v>3779</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>906</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1559</v>
+        <v>1767</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2551</v>
+        <v>859</v>
       </c>
       <c r="C2" t="n">
-        <v>2751</v>
+        <v>6515</v>
       </c>
       <c r="D2" t="n">
-        <v>10203</v>
+        <v>7341</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3821</v>
+        <v>777</v>
       </c>
       <c r="C3" t="n">
-        <v>5871</v>
+        <v>5187</v>
       </c>
       <c r="D3" t="n">
-        <v>14128</v>
+        <v>12957</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3290</v>
+        <v>1171</v>
       </c>
       <c r="C4" t="n">
-        <v>9860</v>
+        <v>4109</v>
       </c>
       <c r="D4" t="n">
-        <v>10794</v>
+        <v>12702</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1785</v>
+        <v>727</v>
       </c>
       <c r="C5" t="n">
-        <v>10553</v>
+        <v>6429</v>
       </c>
       <c r="D5" t="n">
-        <v>4401</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>266</v>
       </c>
       <c r="C6" t="n">
-        <v>6074</v>
+        <v>4994</v>
       </c>
       <c r="D6" t="n">
-        <v>1263</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2949</v>
+        <v>1731</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1116</v>
+        <v>641</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3727</v>
+        <v>395</v>
       </c>
       <c r="C2" t="n">
-        <v>4398</v>
+        <v>2784</v>
       </c>
       <c r="D2" t="n">
-        <v>13070</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2814</v>
+        <v>681</v>
       </c>
       <c r="C3" t="n">
-        <v>4043</v>
+        <v>5145</v>
       </c>
       <c r="D3" t="n">
-        <v>12698</v>
+        <v>11219</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3087</v>
+        <v>817</v>
       </c>
       <c r="C4" t="n">
-        <v>7855</v>
+        <v>4436</v>
       </c>
       <c r="D4" t="n">
-        <v>10977</v>
+        <v>11863</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2107</v>
+        <v>663</v>
       </c>
       <c r="C5" t="n">
-        <v>10135</v>
+        <v>4674</v>
       </c>
       <c r="D5" t="n">
-        <v>5187</v>
+        <v>6566</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>7886</v>
+        <v>4681</v>
       </c>
       <c r="D6" t="n">
-        <v>1680</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>4199</v>
+        <v>2279</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1766</v>
+        <v>714</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>542</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2495</v>
+        <v>258</v>
       </c>
       <c r="C2" t="n">
-        <v>2977</v>
+        <v>3927</v>
       </c>
       <c r="D2" t="n">
-        <v>10040</v>
+        <v>17262</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2710</v>
+        <v>456</v>
       </c>
       <c r="C3" t="n">
-        <v>3841</v>
+        <v>3361</v>
       </c>
       <c r="D3" t="n">
-        <v>12069</v>
+        <v>9562</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2749</v>
+        <v>654</v>
       </c>
       <c r="C4" t="n">
-        <v>6378</v>
+        <v>4745</v>
       </c>
       <c r="D4" t="n">
-        <v>10963</v>
+        <v>11378</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2285</v>
+        <v>669</v>
       </c>
       <c r="C5" t="n">
-        <v>9525</v>
+        <v>4491</v>
       </c>
       <c r="D5" t="n">
-        <v>5740</v>
+        <v>7332</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1255</v>
+        <v>411</v>
       </c>
       <c r="C6" t="n">
-        <v>8869</v>
+        <v>4624</v>
       </c>
       <c r="D6" t="n">
-        <v>1962</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>5316</v>
+        <v>3524</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>921</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2286</v>
+        <v>1472</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>471</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3614</v>
+        <v>402</v>
       </c>
       <c r="C2" t="n">
-        <v>4838</v>
+        <v>5770</v>
       </c>
       <c r="D2" t="n">
-        <v>16469</v>
+        <v>18527</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2222</v>
+        <v>306</v>
       </c>
       <c r="C3" t="n">
-        <v>3162</v>
+        <v>3179</v>
       </c>
       <c r="D3" t="n">
-        <v>11088</v>
+        <v>10151</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2377</v>
+        <v>492</v>
       </c>
       <c r="C4" t="n">
-        <v>5222</v>
+        <v>3915</v>
       </c>
       <c r="D4" t="n">
-        <v>10778</v>
+        <v>10609</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2248</v>
+        <v>598</v>
       </c>
       <c r="C5" t="n">
-        <v>8118</v>
+        <v>4526</v>
       </c>
       <c r="D5" t="n">
-        <v>6162</v>
+        <v>7808</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1458</v>
+        <v>487</v>
       </c>
       <c r="C6" t="n">
-        <v>9037</v>
+        <v>4509</v>
       </c>
       <c r="D6" t="n">
-        <v>2408</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>518</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>6567</v>
+        <v>4050</v>
       </c>
       <c r="D7" t="n">
-        <v>857</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>3317</v>
+        <v>2416</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1110</v>
+        <v>912</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8453</v>
+        <v>3750</v>
       </c>
       <c r="C2" t="n">
-        <v>8622</v>
+        <v>6791</v>
       </c>
       <c r="D2" t="n">
-        <v>16152</v>
+        <v>20689</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2641</v>
+        <v>302</v>
       </c>
       <c r="C2" t="n">
-        <v>2865</v>
+        <v>9372</v>
       </c>
       <c r="D2" t="n">
-        <v>12252</v>
+        <v>21787</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2943</v>
+        <v>288</v>
       </c>
       <c r="C3" t="n">
-        <v>3849</v>
+        <v>3833</v>
       </c>
       <c r="D3" t="n">
-        <v>12394</v>
+        <v>10607</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3291</v>
+        <v>358</v>
       </c>
       <c r="C4" t="n">
-        <v>7855</v>
+        <v>3480</v>
       </c>
       <c r="D4" t="n">
-        <v>10998</v>
+        <v>10211</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1367</v>
+        <v>510</v>
       </c>
       <c r="C5" t="n">
-        <v>12405</v>
+        <v>4150</v>
       </c>
       <c r="D5" t="n">
-        <v>5640</v>
+        <v>7925</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C6" t="n">
-        <v>8029</v>
+        <v>4429</v>
       </c>
       <c r="D6" t="n">
-        <v>1895</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>3250</v>
+        <v>4250</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>1087</v>
+        <v>3103</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>565</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>1507</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>544</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7464</v>
+        <v>4519</v>
       </c>
       <c r="C2" t="n">
-        <v>4623</v>
+        <v>6210</v>
       </c>
       <c r="D2" t="n">
-        <v>15148</v>
+        <v>36725</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3589</v>
+        <v>1211</v>
       </c>
       <c r="C3" t="n">
-        <v>4345</v>
+        <v>2681</v>
       </c>
       <c r="D3" t="n">
-        <v>3352</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5184</v>
+        <v>2427</v>
       </c>
       <c r="C2" t="n">
-        <v>9084</v>
+        <v>2910</v>
       </c>
       <c r="D2" t="n">
-        <v>17102</v>
+        <v>38046</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4543</v>
+        <v>2426</v>
       </c>
       <c r="C3" t="n">
-        <v>3882</v>
+        <v>4106</v>
       </c>
       <c r="D3" t="n">
-        <v>5087</v>
+        <v>9028</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1593</v>
+        <v>586</v>
       </c>
       <c r="C4" t="n">
-        <v>2590</v>
+        <v>1696</v>
       </c>
       <c r="D4" t="n">
-        <v>1856</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5527</v>
+        <v>1609</v>
       </c>
       <c r="C2" t="n">
-        <v>6370</v>
+        <v>5815</v>
       </c>
       <c r="D2" t="n">
-        <v>28699</v>
+        <v>32107</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4006</v>
+        <v>2001</v>
       </c>
       <c r="C3" t="n">
-        <v>5852</v>
+        <v>2941</v>
       </c>
       <c r="D3" t="n">
-        <v>6643</v>
+        <v>13238</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2615</v>
+        <v>1324</v>
       </c>
       <c r="C4" t="n">
-        <v>3230</v>
+        <v>3095</v>
       </c>
       <c r="D4" t="n">
-        <v>2419</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>700</v>
+        <v>297</v>
       </c>
       <c r="C5" t="n">
-        <v>1514</v>
+        <v>1061</v>
       </c>
       <c r="D5" t="n">
-        <v>1270</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5707</v>
+        <v>1948</v>
       </c>
       <c r="C2" t="n">
-        <v>11440</v>
+        <v>5317</v>
       </c>
       <c r="D2" t="n">
-        <v>24770</v>
+        <v>28152</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3877</v>
+        <v>1500</v>
       </c>
       <c r="C3" t="n">
-        <v>5330</v>
+        <v>3902</v>
       </c>
       <c r="D3" t="n">
-        <v>9527</v>
+        <v>15303</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2795</v>
+        <v>1421</v>
       </c>
       <c r="C4" t="n">
-        <v>4516</v>
+        <v>2943</v>
       </c>
       <c r="D4" t="n">
-        <v>3115</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1371</v>
+        <v>689</v>
       </c>
       <c r="C5" t="n">
-        <v>2372</v>
+        <v>2151</v>
       </c>
       <c r="D5" t="n">
-        <v>1417</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357</v>
+        <v>184</v>
       </c>
       <c r="C6" t="n">
-        <v>905</v>
+        <v>681</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6222</v>
+        <v>3456</v>
       </c>
       <c r="C2" t="n">
-        <v>9737</v>
+        <v>7533</v>
       </c>
       <c r="D2" t="n">
-        <v>29685</v>
+        <v>28840</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3493</v>
+        <v>1409</v>
       </c>
       <c r="C3" t="n">
-        <v>6879</v>
+        <v>4030</v>
       </c>
       <c r="D3" t="n">
-        <v>10512</v>
+        <v>16178</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2047</v>
+        <v>1266</v>
       </c>
       <c r="C4" t="n">
-        <v>4021</v>
+        <v>3397</v>
       </c>
       <c r="D4" t="n">
-        <v>3656</v>
+        <v>6761</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1083</v>
+        <v>901</v>
       </c>
       <c r="C5" t="n">
-        <v>2545</v>
+        <v>2496</v>
       </c>
       <c r="D5" t="n">
-        <v>1339</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="C6" t="n">
-        <v>1097</v>
+        <v>1421</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="C7" t="n">
-        <v>390</v>
+        <v>487</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5122</v>
+        <v>2062</v>
       </c>
       <c r="C2" t="n">
-        <v>10143</v>
+        <v>6991</v>
       </c>
       <c r="D2" t="n">
-        <v>25990</v>
+        <v>30416</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4016</v>
+        <v>1888</v>
       </c>
       <c r="C3" t="n">
-        <v>7339</v>
+        <v>5012</v>
       </c>
       <c r="D3" t="n">
-        <v>12959</v>
+        <v>16888</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2419</v>
+        <v>1143</v>
       </c>
       <c r="C4" t="n">
-        <v>5638</v>
+        <v>3648</v>
       </c>
       <c r="D4" t="n">
-        <v>4927</v>
+        <v>8182</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1382</v>
+        <v>955</v>
       </c>
       <c r="C5" t="n">
-        <v>3317</v>
+        <v>2861</v>
       </c>
       <c r="D5" t="n">
-        <v>1730</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>689</v>
+        <v>550</v>
       </c>
       <c r="C6" t="n">
-        <v>1903</v>
+        <v>1922</v>
       </c>
       <c r="D6" t="n">
-        <v>882</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>784</v>
+        <v>926</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>312</v>
+        <v>383</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4951</v>
+        <v>1955</v>
       </c>
       <c r="C2" t="n">
-        <v>11913</v>
+        <v>4306</v>
       </c>
       <c r="D2" t="n">
-        <v>23031</v>
+        <v>23927</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3746</v>
+        <v>2276</v>
       </c>
       <c r="C3" t="n">
-        <v>7665</v>
+        <v>7288</v>
       </c>
       <c r="D3" t="n">
-        <v>14110</v>
+        <v>18896</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2755</v>
+        <v>882</v>
       </c>
       <c r="C4" t="n">
-        <v>6467</v>
+        <v>5057</v>
       </c>
       <c r="D4" t="n">
-        <v>6319</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1650</v>
+        <v>508</v>
       </c>
       <c r="C5" t="n">
-        <v>4495</v>
+        <v>1883</v>
       </c>
       <c r="D5" t="n">
-        <v>2260</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>937</v>
+        <v>197</v>
       </c>
       <c r="C6" t="n">
-        <v>2614</v>
+        <v>907</v>
       </c>
       <c r="D6" t="n">
-        <v>1007</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>1346</v>
+        <v>375</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>547</v>
+        <v>275</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
